--- a/Example/seikyusyo.xlsx
+++ b/Example/seikyusyo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\OysterReport\Example\OysterReport.ExcelToPdfSample\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\OysterReport\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D8B07C-EE18-442C-BCFD-1BA09684269D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40050" yWindow="1665" windowWidth="21480" windowHeight="17940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1725" yWindow="3885" windowWidth="22575" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書" sheetId="1" r:id="rId1"/>
@@ -835,8 +835,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3715099" y="2407819"/>
-          <a:ext cx="2076100" cy="640181"/>
+          <a:off x="3734149" y="2484019"/>
+          <a:ext cx="2076100" cy="643356"/>
           <a:chOff x="3962400" y="2381250"/>
           <a:chExt cx="1885950" cy="628650"/>
         </a:xfrm>

--- a/Example/seikyusyo.xlsx
+++ b/Example/seikyusyo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\OysterReport\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D8B07C-EE18-442C-BCFD-1BA09684269D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E038AD67-E0B2-4DAD-84A3-8A9B8AA7D0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1725" yWindow="3885" windowWidth="22575" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41340" yWindow="3240" windowWidth="19830" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>御中</t>
     <rPh sb="0" eb="2">
@@ -207,6 +207,14 @@
     <rPh sb="0" eb="2">
       <t>ジュウショ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Bold</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Italic</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -218,7 +226,7 @@
     <numFmt numFmtId="5" formatCode="&quot;¥&quot;#,##0;&quot;¥&quot;\-#,##0"/>
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -306,6 +314,22 @@
       <b/>
       <sz val="9"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -439,7 +463,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -562,6 +586,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -835,8 +865,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3734149" y="2484019"/>
-          <a:ext cx="2076100" cy="643356"/>
+          <a:off x="3715099" y="2407819"/>
+          <a:ext cx="2076100" cy="640181"/>
           <a:chOff x="3962400" y="2381250"/>
           <a:chExt cx="1885950" cy="628650"/>
         </a:xfrm>
@@ -1389,11 +1419,18 @@
     </row>
     <row r="2" spans="1:5" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="43" t="s">
+        <v>22</v>
+      </c>
       <c r="E3" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="44"/>
       <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
@@ -1433,8 +1470,6 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
       <c r="E11" s="4" t="s">
         <v>21</v>
       </c>
@@ -1887,7 +1922,7 @@
     <mergeCell ref="A8:B9"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>

--- a/Example/seikyusyo.xlsx
+++ b/Example/seikyusyo.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\OysterReport\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E038AD67-E0B2-4DAD-84A3-8A9B8AA7D0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEF9BC9-40A3-4935-8FAC-0761D15F7F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41340" yWindow="3240" windowWidth="19830" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43050" yWindow="2505" windowWidth="19125" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">請求書!$A$1:$E$58</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -545,6 +548,9 @@
     <xf numFmtId="176" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -578,6 +584,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -586,12 +595,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1419,7 +1422,7 @@
     </row>
     <row r="2" spans="1:5" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="29" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="6" t="s">
@@ -1427,10 +1430,10 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="44"/>
+      <c r="B4" s="41"/>
       <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
@@ -1441,10 +1444,10 @@
       <c r="C5" s="10"/>
     </row>
     <row r="6" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="10"/>
       <c r="D6" s="9"/>
     </row>
@@ -1453,12 +1456,12 @@
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="35"/>
-      <c r="B8" s="35"/>
+      <c r="A8" s="36"/>
+      <c r="B8" s="36"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9" s="36"/>
-      <c r="B9" s="36"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="37"/>
       <c r="C9" s="2" t="s">
         <v>0</v>
       </c>
@@ -1478,57 +1481,57 @@
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
       <c r="E13" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
       <c r="E14" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
       <c r="E15" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="35" t="s">
+      <c r="A16" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
     </row>
     <row r="18" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="38">
         <f>E49</f>
         <v>0</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="39"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="42"/>
+      <c r="A19" s="40"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="44"/>
     </row>
     <row r="20" spans="1:5" ht="13.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1835,69 +1838,69 @@
       </c>
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="29" t="s">
+      <c r="A50" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
-      <c r="E50" s="29"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
     </row>
     <row r="51" spans="1:5" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="30"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
+      <c r="A51" s="31"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="30"/>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
+      <c r="A52" s="31"/>
+      <c r="B52" s="31"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="30"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
+      <c r="A53" s="31"/>
+      <c r="B53" s="31"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="31"/>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31"/>
+      <c r="A54" s="32"/>
+      <c r="B54" s="32"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
     </row>
     <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="32"/>
-      <c r="B55" s="32"/>
-      <c r="C55" s="32"/>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32"/>
+      <c r="A55" s="33"/>
+      <c r="B55" s="33"/>
+      <c r="C55" s="33"/>
+      <c r="D55" s="33"/>
+      <c r="E55" s="33"/>
     </row>
     <row r="56" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="32"/>
-      <c r="B56" s="32"/>
-      <c r="C56" s="32"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="32"/>
+      <c r="A56" s="33"/>
+      <c r="B56" s="33"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="33"/>
     </row>
     <row r="57" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="32"/>
-      <c r="B57" s="32"/>
-      <c r="C57" s="32"/>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32"/>
+      <c r="A57" s="33"/>
+      <c r="B57" s="33"/>
+      <c r="C57" s="33"/>
+      <c r="D57" s="33"/>
+      <c r="E57" s="33"/>
     </row>
     <row r="58" spans="1:5" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="33"/>
-      <c r="B58" s="33"/>
-      <c r="C58" s="33"/>
-      <c r="D58" s="33"/>
-      <c r="E58" s="33"/>
+      <c r="A58" s="34"/>
+      <c r="B58" s="34"/>
+      <c r="C58" s="34"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="34"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="18"/>
@@ -1915,6 +1918,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
     <mergeCell ref="A50:E50"/>
     <mergeCell ref="A51:E54"/>
     <mergeCell ref="A55:E58"/>
@@ -1922,11 +1930,6 @@
     <mergeCell ref="A8:B9"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="C18:C19"/>
   </mergeCells>

--- a/Example/seikyusyo.xlsx
+++ b/Example/seikyusyo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\OysterReport\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEF9BC9-40A3-4935-8FAC-0761D15F7F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22B20D8-A905-4BB9-9E55-1ADE82206607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43050" yWindow="2505" windowWidth="19125" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41700" yWindow="5970" windowWidth="22575" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>御中</t>
     <rPh sb="0" eb="2">
@@ -48,21 +48,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>担当：</t>
-    <rPh sb="0" eb="2">
-      <t>タントウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>FAX：</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TEL：</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>数量</t>
     <rPh sb="0" eb="2">
       <t>スウリョウ</t>
@@ -98,20 +83,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>発行日</t>
-    <rPh sb="0" eb="2">
-      <t>ハッコウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ビ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>No</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>消費税</t>
     <rPh sb="0" eb="3">
       <t>ショウヒゼイ</t>
@@ -213,11 +184,76 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Bold</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Italic</t>
+    <t>TEL：00-0000-0000</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FAX：00-0000-0000</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>担当：○○○○</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>発行日  {{IssueDate}}</t>
+    <rPh sb="0" eb="2">
+      <t>ハッコウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>No {{IssueNo}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{Title}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{DeliveryDate}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{TotalAmount}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{No}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{Item}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{Qty}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{Price}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{Amount}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{SubTotal}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{Tax}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{BillingTo}}</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -466,7 +502,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -503,9 +539,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="5" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -524,9 +557,6 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -545,11 +575,26 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -584,17 +629,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -840,278 +885,6 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>19399</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>55144</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2095499</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="8" name="グループ化 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="3715099" y="2407819"/>
-          <a:ext cx="2076100" cy="640181"/>
-          <a:chOff x="3962400" y="2381250"/>
-          <a:chExt cx="1885950" cy="628650"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="5" name="正方形/長方形 4">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3962400" y="2381250"/>
-            <a:ext cx="628650" cy="628650"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-          <a:ln w="6350">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="50000"/>
-                <a:lumOff val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="6" name="正方形/長方形 5">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="4591050" y="2381250"/>
-            <a:ext cx="628650" cy="628650"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-          <a:ln w="6350">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="50000"/>
-                <a:lumOff val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="7" name="正方形/長方形 6">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5219700" y="2381250"/>
-            <a:ext cx="628650" cy="628650"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-          <a:ln w="6350">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="50000"/>
-                <a:lumOff val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1381125</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2101125</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>138975</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="正方形/長方形 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5276850" y="1495425"/>
-          <a:ext cx="720000" cy="720000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="6350">
-          <a:solidFill>
-            <a:schemeClr val="tx1">
-              <a:lumMod val="50000"/>
-              <a:lumOff val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1414,28 +1187,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="24"/>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="A1" s="22"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3" s="29" t="s">
-        <v>22</v>
-      </c>
+      <c r="A3" s="26"/>
       <c r="E3" s="6" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="41"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
       <c r="E4" s="7" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
@@ -1444,10 +1213,10 @@
       <c r="C5" s="10"/>
     </row>
     <row r="6" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="35"/>
+      <c r="A6" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="38"/>
       <c r="C6" s="10"/>
       <c r="D6" s="9"/>
     </row>
@@ -1456,12 +1225,14 @@
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="36"/>
-      <c r="B8" s="36"/>
+      <c r="A8" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="39"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9" s="37"/>
-      <c r="B9" s="37"/>
+      <c r="A9" s="40"/>
+      <c r="B9" s="40"/>
       <c r="C9" s="2" t="s">
         <v>0</v>
       </c>
@@ -1469,360 +1240,296 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="E10" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="E11" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="40"/>
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
+        <v>10</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="47"/>
       <c r="E13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="E14" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="E15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+    </row>
+    <row r="18" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="39" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="E14" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="E15" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-    </row>
-    <row r="18" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="38">
-        <f>E49</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>12</v>
+      <c r="B18" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="44" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="40"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="44"/>
+      <c r="A19" s="43"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="45"/>
     </row>
     <row r="20" spans="1:5" ht="13.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="26" t="s">
+      <c r="A21" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="26" t="s">
-        <v>6</v>
+      <c r="B21" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="19">
-        <f t="shared" ref="E22:E46" si="0">C22*D22</f>
-        <v>0</v>
+      <c r="A22" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D23" s="20"/>
+      <c r="E23" s="18"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="11"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D24" s="20"/>
+      <c r="E24" s="18"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D25" s="20"/>
+      <c r="E25" s="18"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D26" s="20"/>
+      <c r="E26" s="18"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D27" s="20"/>
+      <c r="E27" s="18"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D28" s="20"/>
+      <c r="E28" s="18"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D29" s="20"/>
+      <c r="E29" s="18"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D30" s="20"/>
+      <c r="E30" s="18"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D31" s="20"/>
+      <c r="E31" s="18"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D32" s="20"/>
+      <c r="E32" s="18"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D33" s="20"/>
+      <c r="E33" s="18"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D34" s="20"/>
+      <c r="E34" s="18"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D35" s="20"/>
+      <c r="E35" s="18"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D36" s="20"/>
+      <c r="E36" s="18"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="11"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D37" s="20"/>
+      <c r="E37" s="18"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D38" s="20"/>
+      <c r="E38" s="18"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="11"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D39" s="20"/>
+      <c r="E39" s="18"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="11"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D40" s="20"/>
+      <c r="E40" s="18"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D41" s="20"/>
+      <c r="E41" s="18"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="11"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D42" s="20"/>
+      <c r="E42" s="18"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="11"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D43" s="20"/>
+      <c r="E43" s="18"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="11"/>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D44" s="20"/>
+      <c r="E44" s="18"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="11"/>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D45" s="20"/>
+      <c r="E45" s="18"/>
     </row>
     <row r="46" spans="1:5" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="15"/>
-      <c r="B46" s="16"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A46" s="14"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="19"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
       <c r="D47" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" s="21">
-        <f>SUM(E22:E46)</f>
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="E47" s="30" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
-      <c r="D48" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="28">
-        <f>E47*0.1</f>
-        <v>0</v>
+      <c r="D48" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="E48" s="29" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1830,91 +1537,90 @@
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
       <c r="D49" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" s="14">
-        <f>SUM(E47:E48)</f>
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="E49" s="28" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B50" s="30"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
-    </row>
-    <row r="51" spans="1:5" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="31"/>
-      <c r="B51" s="31"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="31"/>
+      <c r="A50" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" s="33"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="33"/>
+    </row>
+    <row r="51" spans="1:5" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="34"/>
+      <c r="B51" s="34"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="34"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="31"/>
-      <c r="B52" s="31"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
+      <c r="A52" s="34"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="34"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="31"/>
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
+      <c r="A53" s="34"/>
+      <c r="B53" s="34"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="32"/>
-      <c r="B54" s="32"/>
-      <c r="C54" s="32"/>
-      <c r="D54" s="32"/>
-      <c r="E54" s="32"/>
+      <c r="A54" s="35"/>
+      <c r="B54" s="35"/>
+      <c r="C54" s="35"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="35"/>
     </row>
     <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="33"/>
-      <c r="B55" s="33"/>
-      <c r="C55" s="33"/>
-      <c r="D55" s="33"/>
-      <c r="E55" s="33"/>
+      <c r="A55" s="36"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="36"/>
     </row>
     <row r="56" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="33"/>
-      <c r="B56" s="33"/>
-      <c r="C56" s="33"/>
-      <c r="D56" s="33"/>
-      <c r="E56" s="33"/>
+      <c r="A56" s="36"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="36"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="36"/>
     </row>
     <row r="57" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="33"/>
-      <c r="B57" s="33"/>
-      <c r="C57" s="33"/>
-      <c r="D57" s="33"/>
-      <c r="E57" s="33"/>
+      <c r="A57" s="36"/>
+      <c r="B57" s="36"/>
+      <c r="C57" s="36"/>
+      <c r="D57" s="36"/>
+      <c r="E57" s="36"/>
     </row>
     <row r="58" spans="1:5" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="34"/>
-      <c r="B58" s="34"/>
-      <c r="C58" s="34"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="34"/>
+      <c r="A58" s="37"/>
+      <c r="B58" s="37"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="37"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="18"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
+      <c r="A59" s="17"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="18"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
+      <c r="A60" s="17"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="14">
